--- a/RNR_수입원가_2026_20260707.xlsx
+++ b/RNR_수입원가_2026_20260707.xlsx
@@ -2356,10 +2356,8 @@
       <c r="T6" s="9" t="n">
         <v>20784342</v>
       </c>
-      <c r="U6" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+      <c r="U6" s="174" t="n">
+        <v>46017</v>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
@@ -2483,10 +2481,8 @@
       <c r="T7" s="9" t="n">
         <v>1352610</v>
       </c>
-      <c r="U7" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-20</t>
-        </is>
+      <c r="U7" s="174" t="n">
+        <v>46011</v>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
@@ -2610,10 +2606,8 @@
       <c r="T8" s="9" t="n">
         <v>756850</v>
       </c>
-      <c r="U8" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-13</t>
-        </is>
+      <c r="U8" s="174" t="n">
+        <v>46004</v>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
@@ -2737,9 +2731,7 @@
       <c r="T9" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U9" s="176" t="n">
-        <v>0</v>
-      </c>
+      <c r="U9" s="176" t="n"/>
       <c r="V9" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -2858,10 +2850,8 @@
       <c r="T10" s="9" t="n">
         <v>37658</v>
       </c>
-      <c r="U10" s="174" t="inlineStr">
-        <is>
-          <t>2025-12-26</t>
-        </is>
+      <c r="U10" s="174" t="n">
+        <v>46017</v>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
@@ -2985,10 +2975,8 @@
       <c r="T11" s="9" t="n">
         <v>399770</v>
       </c>
-      <c r="U11" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-16</t>
-        </is>
+      <c r="U11" s="174" t="n">
+        <v>46038</v>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
@@ -3112,10 +3100,8 @@
       <c r="T12" s="9" t="n">
         <v>831820</v>
       </c>
-      <c r="U12" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-24</t>
-        </is>
+      <c r="U12" s="174" t="n">
+        <v>46105</v>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
@@ -3239,10 +3225,8 @@
       <c r="T13" s="9" t="n">
         <v>19976300</v>
       </c>
-      <c r="U13" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-20</t>
-        </is>
+      <c r="U13" s="174" t="n">
+        <v>46042</v>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
@@ -3366,10 +3350,8 @@
       <c r="T14" s="9" t="n">
         <v>3156262</v>
       </c>
-      <c r="U14" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
+      <c r="U14" s="174" t="n">
+        <v>46030</v>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
@@ -3493,10 +3475,8 @@
       <c r="T15" s="9" t="n">
         <v>722808</v>
       </c>
-      <c r="U15" s="174" t="inlineStr">
-        <is>
-          <t>2026-01-08</t>
-        </is>
+      <c r="U15" s="174" t="n">
+        <v>46030</v>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
@@ -3620,10 +3600,8 @@
       <c r="T16" s="9" t="n">
         <v>1704871</v>
       </c>
-      <c r="U16" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+      <c r="U16" s="174" t="n">
+        <v>46087</v>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
@@ -3747,10 +3725,8 @@
       <c r="T17" s="9" t="n">
         <v>874189</v>
       </c>
-      <c r="U17" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
+      <c r="U17" s="174" t="n">
+        <v>46087</v>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
@@ -3874,10 +3850,8 @@
       <c r="T18" s="9" t="n">
         <v>409790</v>
       </c>
-      <c r="U18" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-04</t>
-        </is>
+      <c r="U18" s="174" t="n">
+        <v>46057</v>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
@@ -4001,10 +3975,8 @@
       <c r="T19" s="9" t="n">
         <v>250080</v>
       </c>
-      <c r="U19" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-18</t>
-        </is>
+      <c r="U19" s="174" t="n">
+        <v>46071</v>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
@@ -4128,10 +4100,8 @@
       <c r="T20" s="9" t="n">
         <v>1752040</v>
       </c>
-      <c r="U20" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-26</t>
-        </is>
+      <c r="U20" s="174" t="n">
+        <v>46079</v>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
@@ -4255,10 +4225,8 @@
       <c r="T21" s="9" t="n">
         <v>42329590</v>
       </c>
-      <c r="U21" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
+      <c r="U21" s="174" t="n">
+        <v>46088</v>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
@@ -4382,10 +4350,8 @@
       <c r="T22" s="9" t="n">
         <v>1493440</v>
       </c>
-      <c r="U22" s="174" t="inlineStr">
-        <is>
-          <t>2026-02-14</t>
-        </is>
+      <c r="U22" s="174" t="n">
+        <v>46067</v>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
@@ -4509,9 +4475,7 @@
       <c r="T23" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U23" s="176" t="n">
-        <v>0</v>
-      </c>
+      <c r="U23" s="176" t="n"/>
       <c r="V23" s="12" t="inlineStr">
         <is>
           <t>-</t>
@@ -4630,10 +4594,8 @@
       <c r="T24" s="9" t="n">
         <v>5395574</v>
       </c>
-      <c r="U24" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
+      <c r="U24" s="174" t="n">
+        <v>46110</v>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
@@ -4757,10 +4719,8 @@
       <c r="T25" s="9" t="n">
         <v>26836</v>
       </c>
-      <c r="U25" s="174" t="inlineStr">
-        <is>
-          <t>2026-03-29</t>
-        </is>
+      <c r="U25" s="174" t="n">
+        <v>46110</v>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
@@ -4884,10 +4844,8 @@
       <c r="T26" s="9" t="n">
         <v>4747530</v>
       </c>
-      <c r="U26" s="174" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
+      <c r="U26" s="174" t="n">
+        <v>46119</v>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
@@ -5011,10 +4969,8 @@
       <c r="T27" s="9" t="n">
         <v>350480</v>
       </c>
-      <c r="U27" s="174" t="inlineStr">
-        <is>
-          <t>2026-04-08</t>
-        </is>
+      <c r="U27" s="174" t="n">
+        <v>46120</v>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
@@ -5138,10 +5094,8 @@
       <c r="T28" s="9" t="n">
         <v>317310</v>
       </c>
-      <c r="U28" s="174" t="inlineStr">
-        <is>
-          <t>2026-04-07</t>
-        </is>
+      <c r="U28" s="174" t="n">
+        <v>46119</v>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
@@ -7079,9 +7033,7 @@
       <c r="T45" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U45" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U45" s="298" t="n"/>
       <c r="V45" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7206,9 +7158,7 @@
       <c r="T46" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U46" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U46" s="298" t="n"/>
       <c r="V46" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7333,9 +7283,7 @@
       <c r="T47" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U47" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U47" s="298" t="n"/>
       <c r="V47" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7460,9 +7408,7 @@
       <c r="T48" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U48" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U48" s="298" t="n"/>
       <c r="V48" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7587,9 +7533,7 @@
       <c r="T49" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U49" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U49" s="298" t="n"/>
       <c r="V49" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7714,9 +7658,7 @@
       <c r="T50" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U50" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U50" s="298" t="n"/>
       <c r="V50" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7847,9 +7789,7 @@
       <c r="T51" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U51" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U51" s="298" t="n"/>
       <c r="V51" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -7974,9 +7914,7 @@
       <c r="T52" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U52" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U52" s="298" t="n"/>
       <c r="V52" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8107,9 +8045,7 @@
       <c r="T53" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U53" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U53" s="298" t="n"/>
       <c r="V53" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8234,9 +8170,7 @@
       <c r="T54" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U54" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U54" s="298" t="n"/>
       <c r="V54" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8361,9 +8295,7 @@
       <c r="T55" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U55" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U55" s="298" t="n"/>
       <c r="V55" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8488,9 +8420,7 @@
       <c r="T56" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U56" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U56" s="298" t="n"/>
       <c r="V56" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8615,9 +8545,7 @@
       <c r="T57" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U57" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U57" s="298" t="n"/>
       <c r="V57" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8742,9 +8670,7 @@
       <c r="T58" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U58" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U58" s="298" t="n"/>
       <c r="V58" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8869,9 +8795,7 @@
       <c r="T59" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U59" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U59" s="298" t="n"/>
       <c r="V59" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -8996,9 +8920,7 @@
       <c r="T60" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U60" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U60" s="298" t="n"/>
       <c r="V60" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -9123,9 +9045,7 @@
       <c r="T61" s="302" t="n">
         <v>0</v>
       </c>
-      <c r="U61" s="298" t="n">
-        <v>0</v>
-      </c>
+      <c r="U61" s="298" t="n"/>
       <c r="V61" s="296" t="inlineStr">
         <is>
           <t>-</t>
@@ -10392,9 +10312,7 @@
       <c r="T72" s="290" t="n">
         <v>0</v>
       </c>
-      <c r="U72" s="286" t="n">
-        <v>0</v>
-      </c>
+      <c r="U72" s="286" t="n"/>
       <c r="V72" s="284" t="inlineStr">
         <is>
           <t>-</t>

--- a/RNR_수입원가_2026_20260707.xlsx
+++ b/RNR_수입원가_2026_20260707.xlsx
@@ -5665,7 +5665,7 @@
       <c r="T33" s="128" t="n">
         <v>52140300</v>
       </c>
-      <c r="U33" s="182" t="n"/>
+      <c r="U33" s="181" t="n"/>
       <c r="V33" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5782,7 +5782,7 @@
       <c r="T34" s="128" t="n">
         <v>118665800</v>
       </c>
-      <c r="U34" s="182" t="n"/>
+      <c r="U34" s="181" t="n"/>
       <c r="V34" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5893,7 +5893,7 @@
       <c r="T35" s="128" t="n">
         <v>14902330</v>
       </c>
-      <c r="U35" s="182" t="n"/>
+      <c r="U35" s="181" t="n"/>
       <c r="V35" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -5998,7 +5998,7 @@
       <c r="T36" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U36" s="182" t="n"/>
+      <c r="U36" s="181" t="n"/>
       <c r="V36" s="129" t="n"/>
       <c r="W36" s="128" t="n">
         <v>0</v>
@@ -6337,7 +6337,7 @@
       <c r="T39" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U39" s="182" t="n"/>
+      <c r="U39" s="181" t="n"/>
       <c r="V39" s="129" t="inlineStr">
         <is>
           <t>-</t>
@@ -6462,7 +6462,7 @@
       <c r="T40" s="128" t="n">
         <v>52536040</v>
       </c>
-      <c r="U40" s="182" t="n"/>
+      <c r="U40" s="181" t="n"/>
       <c r="V40" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6577,7 +6577,7 @@
       <c r="T41" s="128" t="n">
         <v>8891915</v>
       </c>
-      <c r="U41" s="182" t="n"/>
+      <c r="U41" s="181" t="n"/>
       <c r="V41" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6692,7 +6692,7 @@
       <c r="T42" s="128" t="n">
         <v>2096763</v>
       </c>
-      <c r="U42" s="182" t="n"/>
+      <c r="U42" s="181" t="n"/>
       <c r="V42" s="129" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
@@ -6807,7 +6807,7 @@
       <c r="T43" s="128" t="n">
         <v>1959600</v>
       </c>
-      <c r="U43" s="182" t="n">
+      <c r="U43" s="181" t="n">
         <v>46202</v>
       </c>
       <c r="V43" s="129" t="inlineStr">
@@ -6920,7 +6920,7 @@
       <c r="T44" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="U44" s="182" t="n"/>
+      <c r="U44" s="181" t="n"/>
       <c r="V44" s="129" t="inlineStr">
         <is>
           <t>-</t>
@@ -9406,7 +9406,7 @@
       <c r="T64" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U64" s="189" t="n"/>
+      <c r="U64" s="188" t="n"/>
       <c r="V64" s="137" t="n"/>
       <c r="W64" s="136" t="n">
         <v>0</v>
@@ -9511,7 +9511,7 @@
       <c r="T65" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U65" s="189" t="n"/>
+      <c r="U65" s="188" t="n"/>
       <c r="V65" s="137" t="n"/>
       <c r="W65" s="136" t="n">
         <v>0</v>
@@ -9616,7 +9616,7 @@
       <c r="T66" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U66" s="189" t="n"/>
+      <c r="U66" s="188" t="n"/>
       <c r="V66" s="137" t="n"/>
       <c r="W66" s="136" t="n">
         <v>0</v>
@@ -9729,7 +9729,7 @@
       <c r="T67" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U67" s="189" t="n"/>
+      <c r="U67" s="188" t="n"/>
       <c r="V67" s="137" t="n"/>
       <c r="W67" s="136" t="n">
         <v>0</v>
@@ -9840,7 +9840,7 @@
       <c r="T68" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U68" s="189" t="n"/>
+      <c r="U68" s="188" t="n"/>
       <c r="V68" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -9955,7 +9955,7 @@
       <c r="T69" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U69" s="189" t="n"/>
+      <c r="U69" s="188" t="n"/>
       <c r="V69" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10070,7 +10070,7 @@
       <c r="T70" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U70" s="189" t="n"/>
+      <c r="U70" s="188" t="n"/>
       <c r="V70" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10185,7 +10185,7 @@
       <c r="T71" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="U71" s="189" t="n"/>
+      <c r="U71" s="188" t="n"/>
       <c r="V71" s="137" t="inlineStr">
         <is>
           <t>-</t>
@@ -10742,7 +10742,7 @@
         <f>SUBTOTAL(9,T5:T44)</f>
         <v/>
       </c>
-      <c r="U76" s="141" t="n"/>
+      <c r="U76" s="147" t="n"/>
       <c r="V76" s="141" t="n"/>
       <c r="W76" s="142">
         <f>SUBTOTAL(9,W5:W44)</f>
@@ -10813,7 +10813,7 @@
         <f>SUBTOTAL(9,T45:T71)</f>
         <v/>
       </c>
-      <c r="U77" s="141" t="n"/>
+      <c r="U77" s="147" t="n"/>
       <c r="V77" s="141" t="n"/>
       <c r="W77" s="142">
         <f>SUBTOTAL(9,W45:W71)</f>
@@ -10884,7 +10884,7 @@
         <f>SUBTOTAL(9,T72:T75)</f>
         <v/>
       </c>
-      <c r="U78" s="141" t="n"/>
+      <c r="U78" s="147" t="n"/>
       <c r="V78" s="141" t="n"/>
       <c r="W78" s="142">
         <f>SUBTOTAL(9,W72:W75)</f>
@@ -10955,7 +10955,7 @@
         <f>SUBTOTAL(9,T5:T75)</f>
         <v/>
       </c>
-      <c r="U79" s="145" t="n"/>
+      <c r="U79" s="154" t="n"/>
       <c r="V79" s="145" t="n"/>
       <c r="W79" s="146">
         <f>SUBTOTAL(9,W5:W75)</f>

--- a/RNR_수입원가_2026_20260707.xlsx
+++ b/RNR_수입원가_2026_20260707.xlsx
@@ -472,7 +472,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="310">
+  <cellXfs count="312">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1370,6 +1370,12 @@
     </xf>
     <xf numFmtId="3" fontId="20" fillId="10" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="12" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="20" fillId="14" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5627,7 +5633,7 @@
       <c r="H33" s="126" t="n">
         <v>351274</v>
       </c>
-      <c r="I33" s="126" t="n">
+      <c r="I33" s="310" t="n">
         <v>1518</v>
       </c>
       <c r="J33" s="128" t="n">
@@ -5643,10 +5649,10 @@
         <v>8000</v>
       </c>
       <c r="N33" s="129" t="n"/>
-      <c r="O33" s="182" t="n">
+      <c r="O33" s="181" t="n">
         <v>46141</v>
       </c>
-      <c r="P33" s="129" t="inlineStr">
+      <c r="P33" s="124" t="inlineStr">
         <is>
           <t>14008-26-101140M</t>
         </is>
@@ -5666,7 +5672,7 @@
         <v>52140300</v>
       </c>
       <c r="U33" s="181" t="n"/>
-      <c r="V33" s="129" t="inlineStr">
+      <c r="V33" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -5697,7 +5703,7 @@
         <f>ROUND(AA33/AB33,0)</f>
         <v/>
       </c>
-      <c r="AD33" s="129" t="inlineStr">
+      <c r="AD33" s="124" t="inlineStr">
         <is>
           <t>2026-04</t>
         </is>
@@ -5740,7 +5746,7 @@
       <c r="H34" s="126" t="n">
         <v>807233</v>
       </c>
-      <c r="I34" s="126">
+      <c r="I34" s="310">
         <f>IFERROR(VLOOKUP(B34,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
@@ -5760,10 +5766,10 @@
         <v/>
       </c>
       <c r="N34" s="129" t="n"/>
-      <c r="O34" s="182" t="n">
+      <c r="O34" s="181" t="n">
         <v>46157</v>
       </c>
-      <c r="P34" s="129" t="inlineStr">
+      <c r="P34" s="124" t="inlineStr">
         <is>
           <t>14008-26-101168M</t>
         </is>
@@ -5783,7 +5789,7 @@
         <v>118665800</v>
       </c>
       <c r="U34" s="181" t="n"/>
-      <c r="V34" s="129" t="inlineStr">
+      <c r="V34" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -5814,7 +5820,7 @@
         <f>ROUND(AA34/AB34,0)</f>
         <v/>
       </c>
-      <c r="AD34" s="129" t="inlineStr">
+      <c r="AD34" s="124" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5855,7 +5861,7 @@
       <c r="H35" s="126" t="n">
         <v>98800</v>
       </c>
-      <c r="I35" s="126" t="n">
+      <c r="I35" s="310" t="n">
         <v>1502.8</v>
       </c>
       <c r="J35" s="128" t="n">
@@ -5871,10 +5877,10 @@
         <v>7973</v>
       </c>
       <c r="N35" s="129" t="n"/>
-      <c r="O35" s="182" t="n">
+      <c r="O35" s="181" t="n">
         <v>46146</v>
       </c>
-      <c r="P35" s="129" t="inlineStr">
+      <c r="P35" s="124" t="inlineStr">
         <is>
           <t>14008-26-101148M</t>
         </is>
@@ -5894,7 +5900,7 @@
         <v>14902330</v>
       </c>
       <c r="U35" s="181" t="n"/>
-      <c r="V35" s="129" t="inlineStr">
+      <c r="V35" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -5925,7 +5931,7 @@
         <f>ROUND(AA35/AB35,0)</f>
         <v/>
       </c>
-      <c r="AD35" s="129" t="inlineStr">
+      <c r="AD35" s="124" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
@@ -5966,7 +5972,7 @@
       <c r="H36" s="126" t="n">
         <v>90</v>
       </c>
-      <c r="I36" s="126" t="n">
+      <c r="I36" s="310" t="n">
         <v>1502.8</v>
       </c>
       <c r="J36" s="128" t="n">
@@ -6297,7 +6303,7 @@
       <c r="H39" s="126" t="n">
         <v>0</v>
       </c>
-      <c r="I39" s="126">
+      <c r="I39" s="310">
         <f>IFERROR(VLOOKUP(B39,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
@@ -6316,7 +6322,7 @@
         <f>IFERROR(VLOOKUP(B39,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N39" s="129" t="inlineStr">
+      <c r="N39" s="124" t="inlineStr">
         <is>
           <t>JNIOR Model 410 (IPO017, FedEx 4/21 발송분)</t>
         </is>
@@ -6338,7 +6344,7 @@
         <v>0</v>
       </c>
       <c r="U39" s="181" t="n"/>
-      <c r="V39" s="129" t="inlineStr">
+      <c r="V39" s="124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6370,12 +6376,12 @@
         <v/>
       </c>
       <c r="AD39" s="129" t="n"/>
-      <c r="AE39" s="182" t="inlineStr">
+      <c r="AE39" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF39" s="182" t="inlineStr">
+      <c r="AF39" s="181" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -6416,7 +6422,7 @@
       <c r="H40" s="126" t="n">
         <v>346792</v>
       </c>
-      <c r="I40" s="126">
+      <c r="I40" s="310">
         <f>IFERROR(VLOOKUP(B40,RemitTable2,7,FALSE),0)</f>
         <v/>
       </c>
@@ -6435,15 +6441,15 @@
         <f>IFERROR(VLOOKUP(B40,RemitTable2,11,FALSE),0)</f>
         <v/>
       </c>
-      <c r="N40" s="129" t="inlineStr">
+      <c r="N40" s="124" t="inlineStr">
         <is>
           <t>CP4420-RGB 4K Projector 8대 + TPC Touch 8 (롯데 렌탈 4차)</t>
         </is>
       </c>
-      <c r="O40" s="182" t="n">
+      <c r="O40" s="181" t="n">
         <v>46177</v>
       </c>
-      <c r="P40" s="129" t="inlineStr">
+      <c r="P40" s="124" t="inlineStr">
         <is>
           <t>14008-26-101227M</t>
         </is>
@@ -6463,7 +6469,7 @@
         <v>52536040</v>
       </c>
       <c r="U40" s="181" t="n"/>
-      <c r="V40" s="129" t="inlineStr">
+      <c r="V40" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6494,7 +6500,7 @@
         <f>ROUND(AA40/AB40,0)</f>
         <v/>
       </c>
-      <c r="AD40" s="129" t="inlineStr">
+      <c r="AD40" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6535,7 +6541,7 @@
       <c r="H41" s="126" t="n">
         <v>49138.8</v>
       </c>
-      <c r="I41" s="126" t="n">
+      <c r="I41" s="310" t="n">
         <v>1517.3</v>
       </c>
       <c r="J41" s="128" t="n">
@@ -6550,15 +6556,15 @@
       <c r="M41" s="128" t="n">
         <v>6473</v>
       </c>
-      <c r="N41" s="129" t="inlineStr">
+      <c r="N41" s="124" t="inlineStr">
         <is>
           <t>MAG 음향장비 loudspeakers 108EA (롯데컬처웍스)</t>
         </is>
       </c>
-      <c r="O41" s="182" t="n">
+      <c r="O41" s="181" t="n">
         <v>46188</v>
       </c>
-      <c r="P41" s="129" t="inlineStr">
+      <c r="P41" s="124" t="inlineStr">
         <is>
           <t>14008-26-101275M</t>
         </is>
@@ -6578,7 +6584,7 @@
         <v>8891915</v>
       </c>
       <c r="U41" s="181" t="n"/>
-      <c r="V41" s="129" t="inlineStr">
+      <c r="V41" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6609,7 +6615,7 @@
         <f>ROUND(AA41/AB41,0)</f>
         <v/>
       </c>
-      <c r="AD41" s="129" t="inlineStr">
+      <c r="AD41" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6650,7 +6656,7 @@
       <c r="H42" s="126" t="n">
         <v>11587.2</v>
       </c>
-      <c r="I42" s="126" t="n">
+      <c r="I42" s="310" t="n">
         <v>1517.3</v>
       </c>
       <c r="J42" s="128" t="n">
@@ -6665,15 +6671,15 @@
       <c r="M42" s="128" t="n">
         <v>1527</v>
       </c>
-      <c r="N42" s="129" t="inlineStr">
+      <c r="N42" s="124" t="inlineStr">
         <is>
           <t>MAG 음향장비 loudspeakers 29EA (CJ 미래원)</t>
         </is>
       </c>
-      <c r="O42" s="182" t="n">
+      <c r="O42" s="181" t="n">
         <v>46188</v>
       </c>
-      <c r="P42" s="129" t="inlineStr">
+      <c r="P42" s="124" t="inlineStr">
         <is>
           <t>14008-26-101275M</t>
         </is>
@@ -6693,7 +6699,7 @@
         <v>2096763</v>
       </c>
       <c r="U42" s="181" t="n"/>
-      <c r="V42" s="129" t="inlineStr">
+      <c r="V42" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6724,7 +6730,7 @@
         <f>ROUND(AA42/AB42,0)</f>
         <v/>
       </c>
-      <c r="AD42" s="129" t="inlineStr">
+      <c r="AD42" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6765,7 +6771,7 @@
       <c r="H43" s="126" t="n">
         <v>12400</v>
       </c>
-      <c r="I43" s="126" t="n">
+      <c r="I43" s="310" t="n">
         <v>1517.1</v>
       </c>
       <c r="J43" s="128" t="n">
@@ -6780,15 +6786,15 @@
       <c r="M43" s="128" t="n">
         <v>8000</v>
       </c>
-      <c r="N43" s="129" t="inlineStr">
+      <c r="N43" s="124" t="inlineStr">
         <is>
           <t>S20-C2220-BEAB 레이저모듈 2set (CP2220)</t>
         </is>
       </c>
-      <c r="O43" s="182" t="n">
+      <c r="O43" s="181" t="n">
         <v>46202</v>
       </c>
-      <c r="P43" s="129" t="inlineStr">
+      <c r="P43" s="124" t="inlineStr">
         <is>
           <t>14008-26-101317M</t>
         </is>
@@ -6810,7 +6816,7 @@
       <c r="U43" s="181" t="n">
         <v>46202</v>
       </c>
-      <c r="V43" s="129" t="inlineStr">
+      <c r="V43" s="124" t="inlineStr">
         <is>
           <t>조운관세사무소</t>
         </is>
@@ -6841,7 +6847,7 @@
         <f>ROUND(AA43/AB43,0)</f>
         <v/>
       </c>
-      <c r="AD43" s="129" t="inlineStr">
+      <c r="AD43" s="124" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
@@ -6884,7 +6890,7 @@
       <c r="H44" s="126" t="n">
         <v>14730</v>
       </c>
-      <c r="I44" s="126" t="n">
+      <c r="I44" s="310" t="n">
         <v>0</v>
       </c>
       <c r="J44" s="128" t="n">
@@ -6899,7 +6905,7 @@
       <c r="M44" s="128" t="n">
         <v>0</v>
       </c>
-      <c r="N44" s="129" t="inlineStr">
+      <c r="N44" s="124" t="inlineStr">
         <is>
           <t>AIB-3000 Cinema Audio Processor 9EA (롯데 인천검단 6 / CJ미래원 1 / RNR 2)</t>
         </is>
@@ -6921,7 +6927,7 @@
         <v>0</v>
       </c>
       <c r="U44" s="181" t="n"/>
-      <c r="V44" s="129" t="inlineStr">
+      <c r="V44" s="124" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9374,7 +9380,7 @@
       <c r="H64" s="134" t="n">
         <v>180</v>
       </c>
-      <c r="I64" s="134" t="n">
+      <c r="I64" s="311" t="n">
         <v>1518.9</v>
       </c>
       <c r="J64" s="136" t="n">
@@ -9434,15 +9440,15 @@
         <f>ROUND(AA64/AB64,0)</f>
         <v/>
       </c>
-      <c r="AD64" s="137" t="inlineStr">
+      <c r="AD64" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE64" s="189" t="n">
+      <c r="AE64" s="188" t="n">
         <v>46143</v>
       </c>
-      <c r="AF64" s="189" t="n">
+      <c r="AF64" s="188" t="n">
         <v>46507</v>
       </c>
     </row>
@@ -9479,7 +9485,7 @@
       <c r="H65" s="134" t="n">
         <v>250</v>
       </c>
-      <c r="I65" s="134" t="n">
+      <c r="I65" s="311" t="n">
         <v>1502.8</v>
       </c>
       <c r="J65" s="136" t="n">
@@ -9539,15 +9545,15 @@
         <f>ROUND(AA65/AB65,0)</f>
         <v/>
       </c>
-      <c r="AD65" s="137" t="inlineStr">
+      <c r="AD65" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE65" s="189" t="n">
+      <c r="AE65" s="188" t="n">
         <v>46143</v>
       </c>
-      <c r="AF65" s="189" t="n">
+      <c r="AF65" s="188" t="n">
         <v>49795</v>
       </c>
     </row>
@@ -9584,7 +9590,7 @@
       <c r="H66" s="134" t="n">
         <v>500</v>
       </c>
-      <c r="I66" s="134" t="n">
+      <c r="I66" s="311" t="n">
         <v>1525.3</v>
       </c>
       <c r="J66" s="136" t="n">
@@ -9644,17 +9650,17 @@
         <f>ROUND(AA66/AB66,0)</f>
         <v/>
       </c>
-      <c r="AD66" s="137" t="inlineStr">
+      <c r="AD66" s="132" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE66" s="189" t="inlineStr">
+      <c r="AE66" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AF66" s="189" t="inlineStr">
+      <c r="AF66" s="188" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9693,7 +9699,7 @@
       <c r="H67" s="134" t="n">
         <v>540</v>
       </c>
-      <c r="I67" s="134" t="n">
+      <c r="I67" s="311" t="n">
         <v>1516.8</v>
       </c>
       <c r="J67" s="136" t="n">
@@ -9708,7 +9714,7 @@
       <c r="M67" s="136" t="n">
         <v>2118</v>
       </c>
-      <c r="N67" s="137" t="inlineStr">
+      <c r="N67" s="132" t="inlineStr">
         <is>
           <t>TMS-1000 License 6 screens (CGV 안동)</t>
         </is>
@@ -9757,15 +9763,15 @@
         <f>ROUND(AA67/AB67,0)</f>
         <v/>
       </c>
-      <c r="AD67" s="137" t="inlineStr">
+      <c r="AD67" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE67" s="189" t="n">
+      <c r="AE67" s="188" t="n">
         <v>46143</v>
       </c>
-      <c r="AF67" s="189" t="n">
+      <c r="AF67" s="188" t="n">
         <v>46507</v>
       </c>
     </row>
@@ -9804,7 +9810,7 @@
       <c r="H68" s="134" t="n">
         <v>32715</v>
       </c>
-      <c r="I68" s="134" t="n">
+      <c r="I68" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J68" s="136" t="n">
@@ -9819,7 +9825,7 @@
       <c r="M68" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N68" s="137" t="inlineStr">
+      <c r="N68" s="132" t="inlineStr">
         <is>
           <t>EW CP2215/CP2309-RGB 24대 (롯데 영천/CineQ 청라/CGV 동두천 외)</t>
         </is>
@@ -9841,7 +9847,7 @@
         <v>0</v>
       </c>
       <c r="U68" s="188" t="n"/>
-      <c r="V68" s="137" t="inlineStr">
+      <c r="V68" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9872,15 +9878,15 @@
         <f>ROUND(AA68/AB68,0)</f>
         <v/>
       </c>
-      <c r="AD68" s="137" t="inlineStr">
+      <c r="AD68" s="132" t="inlineStr">
         <is>
           <t>2026-06</t>
         </is>
       </c>
-      <c r="AE68" s="189" t="n">
+      <c r="AE68" s="188" t="n">
         <v>46192</v>
       </c>
-      <c r="AF68" s="189" t="n">
+      <c r="AF68" s="188" t="n">
         <v>46752</v>
       </c>
     </row>
@@ -9919,7 +9925,7 @@
       <c r="H69" s="134" t="n">
         <v>450</v>
       </c>
-      <c r="I69" s="134" t="n">
+      <c r="I69" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J69" s="136" t="n">
@@ -9934,7 +9940,7 @@
       <c r="M69" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N69" s="137" t="inlineStr">
+      <c r="N69" s="132" t="inlineStr">
         <is>
           <t>TMS-1000 License Extension 5screens (메가박스 경산 하양)</t>
         </is>
@@ -9956,7 +9962,7 @@
         <v>0</v>
       </c>
       <c r="U69" s="188" t="n"/>
-      <c r="V69" s="137" t="inlineStr">
+      <c r="V69" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -9987,15 +9993,15 @@
         <f>ROUND(AA69/AB69,0)</f>
         <v/>
       </c>
-      <c r="AD69" s="137" t="inlineStr">
+      <c r="AD69" s="132" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="AE69" s="189" t="n">
+      <c r="AE69" s="188" t="n">
         <v>46204</v>
       </c>
-      <c r="AF69" s="189" t="n">
+      <c r="AF69" s="188" t="n">
         <v>46568</v>
       </c>
     </row>
@@ -10034,7 +10040,7 @@
       <c r="H70" s="134" t="n">
         <v>7407.81</v>
       </c>
-      <c r="I70" s="134" t="n">
+      <c r="I70" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J70" s="136" t="n">
@@ -10049,7 +10055,7 @@
       <c r="M70" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N70" s="137" t="inlineStr">
+      <c r="N70" s="132" t="inlineStr">
         <is>
           <t>SR-1000/SX-4000 Warranty Ext 11대 (CGV 진주혁신/합천/구례)</t>
         </is>
@@ -10071,7 +10077,7 @@
         <v>0</v>
       </c>
       <c r="U70" s="188" t="n"/>
-      <c r="V70" s="137" t="inlineStr">
+      <c r="V70" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10102,15 +10108,15 @@
         <f>ROUND(AA70/AB70,0)</f>
         <v/>
       </c>
-      <c r="AD70" s="137" t="inlineStr">
+      <c r="AD70" s="132" t="inlineStr">
         <is>
           <t>2026-05</t>
         </is>
       </c>
-      <c r="AE70" s="189" t="n">
+      <c r="AE70" s="188" t="n">
         <v>46156</v>
       </c>
-      <c r="AF70" s="189" t="n">
+      <c r="AF70" s="188" t="n">
         <v>46752</v>
       </c>
     </row>
@@ -10149,7 +10155,7 @@
       <c r="H71" s="134" t="n">
         <v>3320</v>
       </c>
-      <c r="I71" s="134" t="n">
+      <c r="I71" s="311" t="n">
         <v>0</v>
       </c>
       <c r="J71" s="136" t="n">
@@ -10164,7 +10170,7 @@
       <c r="M71" s="136" t="n">
         <v>0</v>
       </c>
-      <c r="N71" s="137" t="inlineStr">
+      <c r="N71" s="132" t="inlineStr">
         <is>
           <t>TMS License 7사이트 32screens (메가박스 삼천포/CGV 대구수성 외)</t>
         </is>
@@ -10186,7 +10192,7 @@
         <v>0</v>
       </c>
       <c r="U71" s="188" t="n"/>
-      <c r="V71" s="137" t="inlineStr">
+      <c r="V71" s="132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -10217,15 +10223,15 @@
         <f>ROUND(AA71/AB71,0)</f>
         <v/>
       </c>
-      <c r="AD71" s="137" t="inlineStr">
+      <c r="AD71" s="132" t="inlineStr">
         <is>
           <t>2026-07</t>
         </is>
       </c>
-      <c r="AE71" s="189" t="n">
+      <c r="AE71" s="188" t="n">
         <v>46204</v>
       </c>
-      <c r="AF71" s="189" t="n">
+      <c r="AF71" s="188" t="n">
         <v>46568</v>
       </c>
     </row>
@@ -12413,6 +12419,46 @@
       <c r="L29" s="228" t="n"/>
       <c r="M29" s="160" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
+    <row r="35"/>
+    <row r="36"/>
+    <row r="37"/>
+    <row r="38"/>
+    <row r="39"/>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
     <row r="70">
       <c r="M70" s="40" t="n"/>
     </row>
@@ -14123,6 +14169,37 @@
       <c r="L39" s="160" t="n"/>
       <c r="M39" s="160" t="n"/>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50"/>
+    <row r="51"/>
+    <row r="52"/>
+    <row r="53"/>
+    <row r="54"/>
+    <row r="55"/>
+    <row r="56"/>
+    <row r="57"/>
+    <row r="58"/>
+    <row r="59"/>
+    <row r="60"/>
+    <row r="61"/>
+    <row r="62"/>
+    <row r="63"/>
+    <row r="64"/>
+    <row r="65"/>
+    <row r="66"/>
+    <row r="67"/>
+    <row r="68"/>
+    <row r="69"/>
+    <row r="70"/>
     <row r="71">
       <c r="M71" s="40" t="n"/>
     </row>
